--- a/data/trans_orig/IP04D$notiene-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26259</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78505</t>
+          <t>78466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87342</t>
+          <t>87424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70352</t>
+          <t>70851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80906</t>
+          <t>81058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>152169</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166502</t>
+          <t>166499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>22885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45534</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427082</t>
+          <t>426226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440151</t>
+          <t>439618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464971</t>
+          <t>466308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479904</t>
+          <t>480317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>896741</t>
+          <t>897666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>916493</t>
+          <t>917458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155767</t>
+          <t>155467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164480</t>
+          <t>164304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166380</t>
+          <t>165560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171603</t>
+          <t>171607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325690</t>
+          <t>325185</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335336</t>
+          <t>335168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>40810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47066</t>
+          <t>48059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73879</t>
+          <t>74330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>669146</t>
+          <t>670325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>686963</t>
+          <t>687544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>710468</t>
+          <t>710774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>729445</t>
+          <t>729487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1385997</t>
+          <t>1385546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1412810</t>
+          <t>1411817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21969</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37863</t>
+          <t>38066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49774</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>46203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>57642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89501</t>
+          <t>89298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105395</t>
+          <t>105054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>52794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77159</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61014</t>
+          <t>60852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87788</t>
+          <t>87605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120695</t>
+          <t>120414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155998</t>
+          <t>156323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393634</t>
+          <t>394466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418879</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398299</t>
+          <t>398482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425073</t>
+          <t>425235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>800882</t>
+          <t>800557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>836185</t>
+          <t>836466</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>27199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>46318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150034</t>
+          <t>149950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161315</t>
+          <t>161422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154658</t>
+          <t>155046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170132</t>
+          <t>169895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310334</t>
+          <t>309629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329311</t>
+          <t>328748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>105936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95798</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131128</t>
+          <t>128502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182313</t>
+          <t>181435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>228599</t>
+          <t>227202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>592223</t>
+          <t>594245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>622041</t>
+          <t>620618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608883</t>
+          <t>611509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644213</t>
+          <t>643910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211593</t>
+          <t>1212990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1257879</t>
+          <t>1258757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28231</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26447</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48481</t>
+          <t>48661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>47796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58149</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>78760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103688</t>
+          <t>103757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>46194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75471</t>
+          <t>74717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56106</t>
+          <t>56838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93396</t>
+          <t>93551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110377</t>
+          <t>110396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155637</t>
+          <t>157890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385039</t>
+          <t>385793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415002</t>
+          <t>414316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422516</t>
+          <t>422361</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459806</t>
+          <t>459074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>820785</t>
+          <t>818532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>866045</t>
+          <t>866026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125299</t>
+          <t>125214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137911</t>
+          <t>138425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143942</t>
+          <t>144795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165494</t>
+          <t>165212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274736</t>
+          <t>273293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299578</t>
+          <t>300025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>72198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111838</t>
+          <t>113770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86163</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130400</t>
+          <t>128326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167889</t>
+          <t>170497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229499</t>
+          <t>227867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>551901</t>
+          <t>549969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>590278</t>
+          <t>591541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>629922</t>
+          <t>631996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674159</t>
+          <t>674409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1194561</t>
+          <t>1196193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1256171</t>
+          <t>1253563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$notiene-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9328</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5270</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14911</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8824</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4945</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13903</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14804</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9328</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15341</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26392</t>
+          <t>26697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76864</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71281</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80922</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,18%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83545</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>78466</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87424</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>77565</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87432</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76864</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>70851</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81058</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152169</t>
+          <t>151864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166499</t>
+          <t>165806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18995</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12739</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27511</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14561</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9493</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22885</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9492</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21991</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18995</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12846</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26855</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>43813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>474168</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>465652</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>480424</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>630</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>434550</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>426226</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>439618</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>427120</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>439619</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>97,89%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>474168</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>466308</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>480317</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,15%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1311</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>897666</t>
+          <t>898462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>917458</t>
+          <t>917182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5536</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2508</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11345</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2361</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11227</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2214</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6668</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170014</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>166199</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171600</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>161276</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>155467</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>164304</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>155585</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>164451</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170014</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>165560</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171607</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325185</t>
+          <t>325027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335168</t>
+          <t>335116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22197</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39990</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28922</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20748</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37967</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21305</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39198</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22097</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>40810</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>46721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74330</t>
+          <t>73394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>721047</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>711594</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>729387</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>980</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679370</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>670325</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>687544</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>669094</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>686987</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>721047</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>710774</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>729487</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1385546</t>
+          <t>1386482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1411817</t>
+          <t>1413155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15958</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22466</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13879</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8528</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19386</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20082</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15958</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10972</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22411</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>38381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46148</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>58410</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44871</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39364</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50222</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>38668</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>49827</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,38%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52656</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>46203</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>57642</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89298</t>
+          <t>88983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105054</t>
+          <t>104712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73458</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>62134</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>87988</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>64053</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52794</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>76327</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>52772</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>76442</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>11,21%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>73458</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>60852</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>87605</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120414</t>
+          <t>120576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156323</t>
+          <t>156098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>412629</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>398099</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>423953</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>615</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>406740</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>394466</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>417999</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>394351</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>418021</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>88,79%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>412629</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>398482</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>425235</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>87,48%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1203</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>800557</t>
+          <t>800782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>836466</t>
+          <t>836304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21847</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14921</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14053</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9216</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20688</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8998</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20722</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>15415</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>30264</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>27215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>46205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163463</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156119</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>170389</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>156585</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149950</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161422</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>149916</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>161640</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,76%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>163463</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>155046</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>169895</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309629</t>
+          <t>309742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328748</t>
+          <t>328732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>94773</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>129732</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>91985</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>79563</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>105936</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>78028</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>106883</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>111264</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>96101</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>128502</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181435</t>
+          <t>180428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>225587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>628747</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>610279</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>645238</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>608196</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>594245</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>620618</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>593298</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>622153</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>628747</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>611509</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>643910</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1212990</t>
+          <t>1214605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1258757</t>
+          <t>1259764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3086</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12357</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13794</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6017</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26425</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50125</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44375</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53646</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28253</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48661</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>74,77%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54238</t>
+          <t>40189</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47796</t>
+          <t>35536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>95122</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78760</t>
+          <t>84118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103757</t>
+          <t>95560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>60160</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>47925</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74157</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>59849</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>46194</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>74717</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56838</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93551</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>132203</t>
+          <t>114793</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110396</t>
+          <t>98110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157890</t>
+          <t>133792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>414902</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>400905</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>427137</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>560</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>400661</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>385793</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>414316</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>443558</t>
+          <t>377815</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422361</t>
+          <t>365762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459074</t>
+          <t>388584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>844219</t>
+          <t>792717</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818532</t>
+          <t>773718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>866026</t>
+          <t>809400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20873</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13908</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29468</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16050</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10127</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23338</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37610</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>36271</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>46652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146589</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137994</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153554</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>132502</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>125214</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>138425</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>156971</t>
+          <t>133503</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144795</t>
+          <t>126864</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165212</t>
+          <t>139768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>289473</t>
+          <t>280091</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>273293</t>
+          <t>269710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>300025</t>
+          <t>289485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>87640</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>73275</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>105461</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>89694</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>72198</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>113770</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128326</t>
+          <t>91092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>164240</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170497</t>
+          <t>143041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227867</t>
+          <t>186375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>611616</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>593795</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>625981</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>824</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>574045</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>549969</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>591541</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>654768</t>
+          <t>551506</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631996</t>
+          <t>537014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674409</t>
+          <t>564217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1228812</t>
+          <t>1163122</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1196193</t>
+          <t>1140987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1253563</t>
+          <t>1184321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
